--- a/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploContatoUnidades.xlsx
+++ b/sei/web/modulos/cargaEmLote/seiCargaEmLote/exemplos/exemploContatoUnidades.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="119">
   <si>
     <t>0-Seq.</t>
   </si>
@@ -65,6 +65,9 @@
     <t>15-siteUnidade</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>ABC</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t>https://abc.gov.br/</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>ASIMP</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
     <t>imprensa@abc.gov.br</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>PROJUR</t>
   </si>
   <si>
@@ -104,6 +113,9 @@
     <t>procuradoria@abc.gov.br</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>ESPRE</t>
   </si>
   <si>
@@ -113,6 +125,9 @@
     <t>projetos@abc.gov.br</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>SETIN</t>
   </si>
   <si>
@@ -149,6 +164,9 @@
     <t>https://abc.gov.br/inovacao</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>SUTEC</t>
   </si>
   <si>
@@ -161,6 +179,9 @@
     <t>Bloco C, Sala 253</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>SUINV</t>
   </si>
   <si>
@@ -173,6 +194,9 @@
     <t>Bloco C, Sala 255</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>SUSIG</t>
   </si>
   <si>
@@ -188,6 +212,9 @@
     <t>https://abc.gov.br/solucoes</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>SEADM</t>
   </si>
   <si>
@@ -203,6 +230,9 @@
     <t>https://abc.gov.br/institucional</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>SUPRI</t>
   </si>
   <si>
@@ -212,6 +242,9 @@
     <t>supri@abc.gov.br</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>SUOPE</t>
   </si>
   <si>
@@ -221,6 +254,9 @@
     <t>suope@abc.gov.br</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>SUGEP</t>
   </si>
   <si>
@@ -233,6 +269,9 @@
     <t>https://abc.gov.br/quem-somos</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>COIRE</t>
   </si>
   <si>
@@ -245,6 +284,9 @@
     <t>Bloco C, Sala S08</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>COSAU</t>
   </si>
   <si>
@@ -254,6 +296,9 @@
     <t>cosau@abc.gov.br</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>COLAB</t>
   </si>
   <si>
@@ -263,6 +308,9 @@
     <t>colab@abc.gov.br</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>COAPE</t>
   </si>
   <si>
@@ -272,6 +320,9 @@
     <t>coape@abc.gov.br</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>COPLA</t>
   </si>
   <si>
@@ -284,6 +335,9 @@
     <t>https://abc.gov.br/capacita</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>SUFIS</t>
   </si>
   <si>
@@ -296,6 +350,9 @@
     <t>https://abc.gov.br/transparencia</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>COPAR</t>
   </si>
   <si>
@@ -303,6 +360,9 @@
   </si>
   <si>
     <t>copar@abc.gov.br</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>COFIC</t>
@@ -704,24 +764,24 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="0">
-        <v>1</v>
+      <c r="A2" s="0" t="s">
+        <v>16</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="0"/>
       <c r="F2" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="0"/>
       <c r="I2" s="0"/>
@@ -731,33 +791,33 @@
       <c r="M2" s="0"/>
       <c r="N2" s="0"/>
       <c r="O2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="P2" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" s="0">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="H3" s="0"/>
       <c r="I3" s="0"/>
@@ -767,33 +827,33 @@
       <c r="M3" s="0"/>
       <c r="N3" s="0"/>
       <c r="O3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="P3" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="0">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="H4" s="0"/>
       <c r="I4" s="0"/>
@@ -803,31 +863,31 @@
       <c r="M4" s="0"/>
       <c r="N4" s="0"/>
       <c r="O4" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="0">
-        <v>4</v>
+      <c r="A5" s="0" t="s">
+        <v>32</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5" s="0"/>
       <c r="F5" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="0"/>
       <c r="I5" s="0"/>
@@ -837,221 +897,221 @@
       <c r="M5" s="0"/>
       <c r="N5" s="0"/>
       <c r="O5" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="0">
-        <v>5</v>
+      <c r="A6" s="0" t="s">
+        <v>36</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E6" s="0"/>
       <c r="F6" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N6" s="0"/>
       <c r="O6" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P6" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="J7" s="0" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="0">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="K7" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="L7" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="0" t="s">
+      <c r="M7" s="0" t="s">
         <v>46</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="0" t="s">
-        <v>41</v>
       </c>
       <c r="N7" s="0"/>
       <c r="O7" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P7" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="0" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="0">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="K8" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N8" s="0"/>
       <c r="O8" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P8" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="0" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="0">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>38</v>
-      </c>
       <c r="K9" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L9" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N9" s="0"/>
       <c r="O9" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="0">
-        <v>9</v>
+      <c r="A10" s="0" t="s">
+        <v>65</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E10" s="0"/>
       <c r="F10" s="0" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="0"/>
       <c r="I10" s="0"/>
@@ -1061,33 +1121,33 @@
       <c r="M10" s="0"/>
       <c r="N10" s="0"/>
       <c r="O10" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P10" s="0" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="0">
-        <v>10</v>
+      <c r="A11" s="0" t="s">
+        <v>71</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="0"/>
       <c r="I11" s="0"/>
@@ -1097,33 +1157,33 @@
       <c r="M11" s="0"/>
       <c r="N11" s="0"/>
       <c r="O11" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P11" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="0">
-        <v>11</v>
+      <c r="A12" s="0" t="s">
+        <v>75</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D12" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="F12" s="0" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="0"/>
       <c r="I12" s="0"/>
@@ -1133,33 +1193,33 @@
       <c r="M12" s="0"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="0">
-        <v>12</v>
+      <c r="A13" s="0" t="s">
+        <v>79</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="0"/>
       <c r="I13" s="0"/>
@@ -1169,177 +1229,177 @@
       <c r="M13" s="0"/>
       <c r="N13" s="0"/>
       <c r="O13" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P13" s="0" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="0">
-        <v>13</v>
+      <c r="A14" s="0" t="s">
+        <v>84</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E14" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="J14" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="K14" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="0" t="s">
-        <v>39</v>
-      </c>
       <c r="L14" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M14" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P14" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="0">
-        <v>14</v>
+      <c r="A15" s="0" t="s">
+        <v>89</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M15" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N15" s="0"/>
       <c r="O15" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P15" s="0" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="0">
-        <v>15</v>
+      <c r="A16" s="0" t="s">
+        <v>93</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M16" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N16" s="0"/>
       <c r="O16" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="P16" s="0" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="0">
-        <v>16</v>
+      <c r="A17" s="0" t="s">
+        <v>97</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="0"/>
       <c r="I17" s="0"/>
@@ -1349,33 +1409,33 @@
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
       <c r="O17" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="P17" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="0">
-        <v>17</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="G18" s="0" t="s">
-        <v>20</v>
       </c>
       <c r="H18" s="0"/>
       <c r="I18" s="0"/>
@@ -1385,33 +1445,33 @@
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
       <c r="O18" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P18" s="0" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="0">
-        <v>18</v>
+      <c r="A19" s="0" t="s">
+        <v>106</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="0"/>
       <c r="I19" s="0"/>
@@ -1421,33 +1481,33 @@
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>
       <c r="O19" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P19" s="0" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="0">
-        <v>19</v>
+      <c r="A20" s="0" t="s">
+        <v>111</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="0"/>
       <c r="I20" s="0"/>
@@ -1457,33 +1517,33 @@
       <c r="M20" s="0"/>
       <c r="N20" s="0"/>
       <c r="O20" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P20" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="0">
-        <v>20</v>
+      <c r="A21" s="0" t="s">
+        <v>115</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
@@ -1493,10 +1553,10 @@
       <c r="M21" s="0"/>
       <c r="N21" s="0"/>
       <c r="O21" s="0" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="P21" s="0" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
